--- a/templates/PRAP_SourceData_Dummy_10x10_v1.2.xlsx
+++ b/templates/PRAP_SourceData_Dummy_10x10_v1.2.xlsx
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A122"/>
+  <dimension ref="A1:A130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -1088,28 +1088,28 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>ADDING A PERMITTED VALUE</t>
+          <t>ASSIGNMENT DATES ARE OPTIONAL</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
+          <t xml:space="preserve">   Leave assign_start_date and assign_end_date BLANK for somebody who is on the project for</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
+          <t xml:space="preserve">   the whole of it - which is most people. A blank date means the project's own, so the two</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
+          <t xml:space="preserve">   never fall out of step when the project's dates move.</t>
         </is>
       </c>
     </row>
@@ -1117,229 +1117,277 @@
       <c r="A87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Fill them in only for a PARTIAL involvement: somebody who joins late, leaves early, or</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
+          <t xml:space="preserve">   covers one stretch of a longer study.</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
-        </is>
-      </c>
+      <c r="A90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr"/>
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>ADDING A PERMITTED VALUE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
+          <t xml:space="preserve">   Insert a row inside that list's block on the Lists sheet, so the block stays contiguous -</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
+          <t xml:space="preserve">   the dropdowns read a range, not a scattered set of rows. work_scope_type is meant to be</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
+          <t xml:space="preserve">   extended this way: the three values supplied are a starting point, not a closed set.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the same thing three times.</t>
-        </is>
-      </c>
+      <c r="A95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>WORK SCOPE, AND THE EMPTY ROW THAT COVERS EVERY SCOPE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IS IN THIS FILE</t>
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   PeriodWeightStandard and RoleFactor are keyed on work_scope_type as well as on the project</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   10 projects   8 clinical trials (PRJ-001..008) + 2 'Others' (PRJ-009..010)</t>
+          <t xml:space="preserve">   type, the phase and the period. A row with work_scope_type EMPTY applies to EVERY scope.</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   10 people     PSN-001..010, including PSN-004 at 0.80, PSN-010 at 0.60 capacity</t>
-        </is>
-      </c>
+      <c r="A99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   50 assignments, 60 milestones, 50 periods, spanning 50 months (Feb 2025 to Mar 2029)</t>
+          <t xml:space="preserve">   So fill the empty-scope rows first - they are your baseline - and add a scope-specific row</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Types: Biosimilar CT (Healthy), Biosimilar CT (Patient), NewDrug CT.  Phases: Phase 1, Phase 2, Phase 3, Phase 4.</t>
+          <t xml:space="preserve">   only where that scope really does change the number. A project looks for its own scope</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr"/>
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   first and falls back to the empty row, so nothing has to be entered three times to say</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>WHAT IT DEMONSTRATES</t>
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the same thing three times.</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - 5 of the 8 trials carry an interim DB lock, so each has TWO 'Conduct'</t>
-        </is>
-      </c>
+      <c r="A104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     stretches and two close-outs. The other 3 run Conduct once.</t>
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IS IN THIS FILE</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 2 trials record an 'Inspection' after the final DB lock and so carry the</t>
+          <t xml:space="preserve">   10 projects   8 clinical trials (PRJ-001..008) + 2 'Others' (PRJ-009..010)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     seventh period, 'After Close-out (final)'.</t>
+          <t xml:space="preserve">   10 people     PSN-001..010, including PSN-004 at 0.80, PSN-010 at 0.60 capacity</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - The 2 'Others' projects have hand-entered periods and no milestones.</t>
+          <t xml:space="preserve">   50 assignments, 60 milestones, 50 periods, spanning 50 months (Feb 2025 to Mar 2029)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - PSN-001 carries two extra oversight assignments on top of a full round-robin</t>
+          <t xml:space="preserve">   Types: Biosimilar CT (Healthy), Biosimilar CT (Patient), NewDrug CT.  Phases: Phase 1, Phase 2, Phase 3, Phase 4.</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     share, and so crosses the 1.50 FTE ceiling at the peaks.</t>
-        </is>
-      </c>
+      <c r="A110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   - PSN-009 is the busiest by row count, at 8 assignments - every trial, as the only</t>
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>WHAT IT DEMONSTRATES</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Data Analyst. Their share of each is set lower to match.</t>
+          <t xml:space="preserve">   - 5 of the 8 trials carry an interim DB lock, so each has TWO 'Conduct'</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - PSN-010 is a part-timer carrying 2 light assignments, so an under-allocation</t>
+          <t xml:space="preserve">     stretches and two close-outs. The other 3 run Conduct once.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     run is raised. With the floor at 0.60 they CAN clear it, but only at full utilisation -</t>
+          <t xml:space="preserve">   - 2 trials record an 'Inspection' after the final DB lock and so carry the</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     V-22 warns if anyone is recorded below the floor and so could never clear it.</t>
+          <t xml:space="preserve">     seventh period, 'After Close-out (final)'.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - 2 assignments carry PersonPeriodWeight overrides, one of them with 2 separate</t>
+          <t xml:space="preserve">   - The 2 'Others' projects have hand-entered periods and no milestones.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     windows, which is why that sheet is keyed on assignment_id AND period_start.</t>
+          <t xml:space="preserve">   - PSN-001 carries two extra oversight assignments on top of a full round-robin</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - The months at either end of the span are naturally light: with few projects</t>
+          <t xml:space="preserve">     share, and so crosses the 1.50 FTE ceiling at the peaks.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">     overlapping there, most under-allocation runs sit in the ramp-up and wind-down.</t>
+          <t xml:space="preserve">   - PSN-009 is the busiest by row count, at 8 assignments - every trial, as the only</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr"/>
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Data Analyst. Their share of each is set lower to match.</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The weights and role factors here are ILLUSTRATIVE, so the numbers can be exercised.</t>
+          <t xml:space="preserve">   - PSN-010 is a part-timer carrying 2 light assignments, so an under-allocation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     run is raised. With the floor at 0.60 they CAN clear it, but only at full utilisation -</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     V-22 warns if anyone is recorded below the floor and so could never clear it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - 2 assignments carry PersonPeriodWeight overrides, one of them with 2 separate</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     windows, which is why that sheet is keyed on assignment_id AND period_start.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   - The months at either end of the span are naturally light: with few projects</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     overlapping there, most under-allocation runs sit in the ramp-up and wind-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   The weights and role factors here are ILLUSTRATIVE, so the numbers can be exercised.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Replace them with your own before drawing any conclusion from the output.</t>
         </is>
@@ -54262,14 +54310,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F2" s="8" t="n">
-        <v>45717</v>
-      </c>
-      <c r="G2" s="8" t="n">
-        <v>46384</v>
-      </c>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
       <c r="H2" s="7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I2" s="7" t="n"/>
       <c r="J2" s="7" t="n"/>
@@ -54307,7 +54351,7 @@
         <v>46446</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="n"/>
@@ -54342,10 +54386,10 @@
         <v>45778</v>
       </c>
       <c r="G4" s="8" t="n">
-        <v>46384</v>
+        <v>46446</v>
       </c>
       <c r="H4" s="7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
@@ -54376,14 +54420,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n">
-        <v>45717</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <v>46384</v>
-      </c>
+      <c r="F5" s="8" t="n"/>
+      <c r="G5" s="8" t="n"/>
       <c r="H5" s="7" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
@@ -54418,10 +54458,10 @@
         <v>45778</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>46446</v>
+        <v>46415</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
@@ -54456,10 +54496,10 @@
         <v>46023</v>
       </c>
       <c r="G7" s="8" t="n">
-        <v>46873</v>
+        <v>46812</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
@@ -54490,14 +54530,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>46873</v>
-      </c>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
       <c r="H8" s="7" t="n">
-        <v>0.28</v>
+        <v>0.36</v>
       </c>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
@@ -54532,10 +54568,10 @@
         <v>46023</v>
       </c>
       <c r="G9" s="8" t="n">
-        <v>46842</v>
+        <v>46873</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
@@ -54567,13 +54603,13 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>46023</v>
+        <v>45992</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>46842</v>
+        <v>46873</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
@@ -54604,14 +54640,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>46812</v>
-      </c>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
       <c r="H11" s="7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
@@ -54643,13 +54675,13 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46082</v>
+        <v>46023</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>46934</v>
+        <v>46903</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
@@ -54681,13 +54713,13 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>46903</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="I13" s="7" t="n"/>
       <c r="J13" s="7" t="n"/>
@@ -54718,14 +54750,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
       <c r="H14" s="7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I14" s="7" t="n"/>
       <c r="J14" s="7" t="n"/>
@@ -54757,13 +54785,13 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>46873</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="I15" s="7" t="n"/>
       <c r="J15" s="7" t="n"/>
@@ -54795,13 +54823,13 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>46023</v>
+        <v>46082</v>
       </c>
       <c r="G16" s="8" t="n">
-        <v>46903</v>
+        <v>46934</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="I16" s="7" t="n"/>
       <c r="J16" s="7" t="n"/>
@@ -54832,14 +54860,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n">
-        <v>45839</v>
-      </c>
-      <c r="G17" s="8" t="n">
-        <v>46690</v>
-      </c>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
       <c r="H17" s="7" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="I17" s="7" t="n"/>
       <c r="J17" s="7" t="n"/>
@@ -54871,13 +54895,13 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>45870</v>
+        <v>45809</v>
       </c>
       <c r="G18" s="8" t="n">
-        <v>46690</v>
+        <v>46721</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>0.35</v>
+        <v>0.28</v>
       </c>
       <c r="I18" s="7" t="n"/>
       <c r="J18" s="7" t="n"/>
@@ -54909,13 +54933,13 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>46721</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="I19" s="7" t="n"/>
       <c r="J19" s="7" t="n"/>
@@ -54946,14 +54970,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
-        <v>45809</v>
-      </c>
-      <c r="G20" s="8" t="n">
-        <v>46660</v>
-      </c>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
       <c r="H20" s="7" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="I20" s="7" t="n"/>
       <c r="J20" s="7" t="n"/>
@@ -54988,7 +55008,7 @@
         <v>45809</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>46660</v>
+        <v>46690</v>
       </c>
       <c r="H21" s="7" t="n">
         <v>0.13</v>
@@ -55023,13 +55043,13 @@
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>46873</v>
+        <v>46903</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I22" s="7" t="n"/>
       <c r="J22" s="7" t="n"/>
@@ -55060,14 +55080,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
-        <v>46054</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>46903</v>
-      </c>
+      <c r="F23" s="8" t="n"/>
+      <c r="G23" s="8" t="n"/>
       <c r="H23" s="7" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="I23" s="7" t="n"/>
       <c r="J23" s="7" t="n"/>
@@ -55102,10 +55118,10 @@
         <v>46082</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>46873</v>
+        <v>46903</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="I24" s="7" t="n"/>
       <c r="J24" s="7" t="n"/>
@@ -55137,13 +55153,13 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>46054</v>
+        <v>46023</v>
       </c>
       <c r="G25" s="8" t="n">
-        <v>46873</v>
+        <v>46934</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="I25" s="7" t="n"/>
       <c r="J25" s="7" t="n"/>
@@ -55174,12 +55190,8 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F26" s="8" t="n">
-        <v>46023</v>
-      </c>
-      <c r="G26" s="8" t="n">
-        <v>46934</v>
-      </c>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
       <c r="H26" s="7" t="n">
         <v>0.14</v>
       </c>
@@ -55213,13 +55225,13 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G27" s="8" t="n">
         <v>46356</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="I27" s="7" t="n"/>
       <c r="J27" s="7" t="n"/>
@@ -55251,13 +55263,13 @@
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="G28" s="8" t="n">
-        <v>46356</v>
+        <v>46418</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="I28" s="7" t="n"/>
       <c r="J28" s="7" t="n"/>
@@ -55288,14 +55300,10 @@
           <t>Clinical Data Associator</t>
         </is>
       </c>
-      <c r="F29" s="8" t="n">
-        <v>45748</v>
-      </c>
-      <c r="G29" s="8" t="n">
-        <v>46418</v>
-      </c>
+      <c r="F29" s="8" t="n"/>
+      <c r="G29" s="8" t="n"/>
       <c r="H29" s="7" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="I29" s="7" t="n"/>
       <c r="J29" s="7" t="n"/>
@@ -55327,13 +55335,13 @@
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>45748</v>
+        <v>45689</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>46418</v>
+        <v>46387</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="I30" s="7" t="n"/>
       <c r="J30" s="7" t="n"/>
@@ -55365,13 +55373,13 @@
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="G31" s="8" t="n">
         <v>46356</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="I31" s="7" t="n"/>
       <c r="J31" s="7" t="n"/>
@@ -55402,14 +55410,10 @@
           <t>Project oversight</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>45931</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>47149</v>
-      </c>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
       <c r="H32" s="7" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="I32" s="7" t="n"/>
       <c r="J32" s="7" t="n"/>
@@ -55444,10 +55448,10 @@
         <v>45992</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>47208</v>
+        <v>47177</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>0.35</v>
+        <v>0.29</v>
       </c>
       <c r="I33" s="7" t="n"/>
       <c r="J33" s="7" t="n"/>
@@ -55479,13 +55483,13 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G34" s="8" t="n">
-        <v>47177</v>
+        <v>47149</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
       <c r="I34" s="7" t="n"/>
       <c r="J34" s="7" t="n"/>
@@ -55516,14 +55520,10 @@
           <t>Clinical Database Programmer</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>47149</v>
-      </c>
+      <c r="F35" s="8" t="n"/>
+      <c r="G35" s="8" t="n"/>
       <c r="H35" s="7" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="I35" s="7" t="n"/>
       <c r="J35" s="7" t="n"/>
@@ -55555,13 +55555,13 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>45931</v>
+        <v>45992</v>
       </c>
       <c r="G36" s="8" t="n">
-        <v>47149</v>
+        <v>47177</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="I36" s="7" t="n"/>
       <c r="J36" s="7" t="n"/>
@@ -55596,10 +55596,10 @@
         <v>45992</v>
       </c>
       <c r="G37" s="8" t="n">
-        <v>47149</v>
+        <v>47208</v>
       </c>
       <c r="H37" s="7" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="I37" s="7" t="n"/>
       <c r="J37" s="7" t="n"/>
@@ -55630,14 +55630,10 @@
           <t>Lead data manager</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>45962</v>
-      </c>
-      <c r="G38" s="8" t="n">
-        <v>47208</v>
-      </c>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
       <c r="H38" s="7" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="I38" s="7" t="n"/>
       <c r="J38" s="7" t="n"/>
@@ -55675,7 +55671,7 @@
         <v>47208</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I39" s="7" t="n"/>
       <c r="J39" s="7" t="n"/>
@@ -55707,13 +55703,13 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="G40" s="8" t="n">
-        <v>47177</v>
+        <v>47149</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="I40" s="7" t="n"/>
       <c r="J40" s="7" t="n"/>
@@ -55744,14 +55740,10 @@
           <t>Data Analyst</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>45992</v>
-      </c>
-      <c r="G41" s="8" t="n">
-        <v>47149</v>
-      </c>
+      <c r="F41" s="8" t="n"/>
+      <c r="G41" s="8" t="n"/>
       <c r="H41" s="7" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="I41" s="7" t="n"/>
       <c r="J41" s="7" t="n"/>
@@ -55789,7 +55781,7 @@
         <v>46568</v>
       </c>
       <c r="H42" s="7" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="I42" s="7" t="n"/>
       <c r="J42" s="7" t="n"/>
@@ -55821,13 +55813,13 @@
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>46478</v>
+        <v>46419</v>
       </c>
       <c r="G43" s="8" t="n">
-        <v>46599</v>
+        <v>46538</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="I43" s="7" t="n"/>
       <c r="J43" s="7" t="n"/>
@@ -55858,14 +55850,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F44" s="8" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>46599</v>
-      </c>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
       <c r="H44" s="7" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="I44" s="7" t="n"/>
       <c r="J44" s="7" t="n"/>
@@ -55897,13 +55885,13 @@
         </is>
       </c>
       <c r="F45" s="8" t="n">
-        <v>46388</v>
+        <v>46419</v>
       </c>
       <c r="G45" s="8" t="n">
-        <v>46598</v>
+        <v>46660</v>
       </c>
       <c r="H45" s="7" t="n">
-        <v>0.38</v>
+        <v>0.28</v>
       </c>
       <c r="I45" s="7" t="n"/>
       <c r="J45" s="7" t="n"/>
@@ -55938,10 +55926,10 @@
         <v>46447</v>
       </c>
       <c r="G46" s="8" t="n">
-        <v>46629</v>
+        <v>46598</v>
       </c>
       <c r="H46" s="7" t="n">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="I46" s="7" t="n"/>
       <c r="J46" s="7" t="n"/>
@@ -55972,14 +55960,10 @@
           <t>Other staff</t>
         </is>
       </c>
-      <c r="F47" s="8" t="n">
-        <v>46447</v>
-      </c>
-      <c r="G47" s="8" t="n">
-        <v>46660</v>
-      </c>
+      <c r="F47" s="8" t="n"/>
+      <c r="G47" s="8" t="n"/>
       <c r="H47" s="7" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="I47" s="7" t="n"/>
       <c r="J47" s="7" t="n"/>
